--- a/docs/menu.xlsx
+++ b/docs/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\family-ledger_RevB\Lunch_HP\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E456495C-E521-4772-9EC1-DA696C8C4384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5502F455-FF9A-4F6F-9729-75DEE6E9FEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{504593EE-F976-48B5-AFB4-FB9E953D2C73}"/>
   </bookViews>
@@ -41,24 +41,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
-    <t>豪華三拼牛肉雞胸蝦仁烤蔬套餐</t>
-  </si>
-  <si>
     <t>木桑森林</t>
   </si>
   <si>
-    <t>香滷牛肉烤蔬套餐</t>
-  </si>
-  <si>
-    <t>藤椒雞腿肉烤蔬套餐</t>
-  </si>
-  <si>
-    <t>滷牛肉+雞胸肉烤蔬套餐</t>
-  </si>
-  <si>
-    <t>香煎雞胸肉烤蔬套餐</t>
-  </si>
-  <si>
     <t>麦辣鸡腿堡</t>
   </si>
   <si>
@@ -92,9 +77,6 @@
     <t>必胜客</t>
   </si>
   <si>
-    <t>照燒雞排便當</t>
-  </si>
-  <si>
     <t>筑地屋</t>
   </si>
   <si>
@@ -116,39 +98,21 @@
     <t>谷田稻香</t>
   </si>
   <si>
-    <t>單點西藍花</t>
-  </si>
-  <si>
     <t>浓香猪脚煲套餐</t>
   </si>
   <si>
-    <t>金湯酸菜魚套餐</t>
-  </si>
-  <si>
     <t>肉末茄子套餐</t>
   </si>
   <si>
-    <t>台式滷肉套餐</t>
-  </si>
-  <si>
     <t>梅菜扣肉套餐</t>
   </si>
   <si>
     <t>黑胡椒牛肉套餐</t>
   </si>
   <si>
-    <t>單點原味大鸡排</t>
-  </si>
-  <si>
     <t>享德来</t>
   </si>
   <si>
-    <t>單點藤椒腿排</t>
-  </si>
-  <si>
-    <t>雞排飯</t>
-  </si>
-  <si>
     <t>咕咾肉便当</t>
   </si>
   <si>
@@ -170,12 +134,6 @@
     <t>全素</t>
   </si>
   <si>
-    <t>魚香肉絲</t>
-  </si>
-  <si>
-    <t xml:space="preserve">梅菜扣肉饭 </t>
-  </si>
-  <si>
     <t>咖喱牛肉饭</t>
   </si>
   <si>
@@ -185,18 +143,6 @@
     <t>香辣牛肉</t>
   </si>
   <si>
-    <t>紅燒排骨</t>
-  </si>
-  <si>
-    <t>香酥排骨飯</t>
-  </si>
-  <si>
-    <t>香腸飯</t>
-  </si>
-  <si>
-    <t>雞腿飯</t>
-  </si>
-  <si>
     <t>价格（RMB）</t>
   </si>
   <si>
@@ -207,6 +153,60 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>鸡腿饭</t>
+  </si>
+  <si>
+    <t>香肠饭</t>
+  </si>
+  <si>
+    <t>香酥排骨饭</t>
+  </si>
+  <si>
+    <t>红烧排骨</t>
+  </si>
+  <si>
+    <t>梅菜扣肉饭</t>
+  </si>
+  <si>
+    <t>鱼香肉丝</t>
+  </si>
+  <si>
+    <t>鸡排饭</t>
+  </si>
+  <si>
+    <t>单点藤椒腿排</t>
+  </si>
+  <si>
+    <t>单点原味大鸡排</t>
+  </si>
+  <si>
+    <t>台式卤肉套餐</t>
+  </si>
+  <si>
+    <t>金汤酸菜鱼套餐</t>
+  </si>
+  <si>
+    <t>单点西蓝花</t>
+  </si>
+  <si>
+    <t>照烧鸡排便当</t>
+  </si>
+  <si>
+    <t>香煎鸡胸肉烤蔬套餐</t>
+  </si>
+  <si>
+    <t>卤牛肉+鸡胸肉烤蔬套餐</t>
+  </si>
+  <si>
+    <t>藤椒鸡腿肉烤蔬套餐</t>
+  </si>
+  <si>
+    <t>香卤牛肉烤蔬套餐</t>
+  </si>
+  <si>
+    <t>豪华三拼牛肉鸡胸虾仁烤蔬套餐</t>
   </si>
 </sst>
 </file>
@@ -526,19 +526,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC384EE4-3741-412A-B1A2-F9BFA5BC0865}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="29.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -546,10 +549,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>27</v>
@@ -560,10 +563,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>27</v>
@@ -574,10 +577,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>26</v>
@@ -588,10 +591,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D5">
         <v>27</v>
@@ -602,10 +605,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>47</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -616,10 +619,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>27</v>
@@ -630,10 +633,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>30</v>
@@ -644,10 +647,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9">
         <v>29</v>
@@ -658,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
@@ -672,10 +675,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D11">
         <v>18</v>
@@ -686,10 +689,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>18</v>
@@ -700,10 +703,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>26</v>
@@ -714,10 +717,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>26</v>
@@ -728,10 +731,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>23</v>
@@ -742,10 +745,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -756,10 +759,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>26</v>
@@ -770,10 +773,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D18">
         <v>20</v>
@@ -784,10 +787,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D19">
         <v>12</v>
@@ -798,10 +801,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -812,10 +815,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>37</v>
@@ -826,10 +829,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D22">
         <v>30</v>
@@ -840,10 +843,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D23">
         <v>30</v>
@@ -854,10 +857,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D24">
         <v>24</v>
@@ -868,10 +871,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D25">
         <v>34</v>
@@ -882,10 +885,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D26">
         <v>37</v>
@@ -896,10 +899,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -910,10 +913,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>39</v>
@@ -924,10 +927,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -938,10 +941,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>48</v>
@@ -952,10 +955,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D31">
         <v>50</v>
@@ -966,10 +969,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D32">
         <v>50</v>
@@ -980,10 +983,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D33">
         <v>42</v>
@@ -994,10 +997,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>69</v>
@@ -1008,10 +1011,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>89</v>
@@ -1022,10 +1025,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>88</v>
@@ -1036,10 +1039,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>27</v>
@@ -1050,10 +1053,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>29</v>
@@ -1064,10 +1067,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>27</v>
@@ -1078,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>59</v>
@@ -1092,10 +1095,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>43.5</v>
@@ -1106,10 +1109,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>42.5</v>
@@ -1120,10 +1123,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="D43">
         <v>20</v>
@@ -1134,10 +1137,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="D44">
         <v>28</v>
@@ -1148,10 +1151,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D45">
         <v>22</v>
@@ -1162,10 +1165,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D46">
         <v>30</v>
@@ -1176,10 +1179,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D47">
         <v>32</v>
